--- a/public/Plantilla_Ecometrics_IRM_Final.xlsx
+++ b/public/Plantilla_Ecometrics_IRM_Final.xlsx
@@ -334,6 +334,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -638,7 +641,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -687,7 +691,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>⚠  Usa los menús desplegables en columnas MATERIAL y CLIENTE.  La FECHA debe corresponder al mes del período seleccionado en Ecometrics.</t>
+          <t>⚠ Usa los menús desplegables en MATERIAL y CLIENTE. La FECHA debe corresponder al mes seleccionado. Si cuentas con IMPORTE PAGADO, llénalo para que Ecometrics calcule el impacto económico exacto.</t>
         </is>
       </c>
     </row>
@@ -715,6 +719,16 @@
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>NOTAS</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>PRECIO</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>IMPORTE PAGADO</t>
         </is>
       </c>
     </row>
